--- a/docs/【キャラ_003】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_003】ときめきポケット_03稿.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>20を「中学三年生」（漢数字）に統一</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>48を「三か月」に統一</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>59を「プランA」（半角）に統一</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>半角に統一（3話32・5話10を「5、4、3、2、1、ゼロ」、5話76を「1メートル」に）</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>「！？」に統一</t>
+          <t>「！？」（全角2文字）に統一</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>空白を削除、または全角スペースに統一</t>
+          <t>1話29・34の行頭の半角スペースを削除、1話52「へ？ 」の半角スペースを全角スペースに。1話63・5話45：行末の空白を削除</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -2206,6 +2206,46 @@
       <c r="H38" s="6" t="inlineStr">
         <is>
           <t>演出で対応済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>1話・2話</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1話11 / 2話98</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>1話11 / 2話98</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>書式</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>1話11・2話98『結城 奏』の名前の中の半角スペース</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>姓と名の区切りとして残す（omen決定）</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>対応不要</t>
         </is>
       </c>
     </row>
@@ -2649,10 +2689,10 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>結城さんは物静かで、
-そう言う事には関心がないと思っていた</t>
+そういう事には関心がないと思っていた</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
@@ -2769,9 +2809,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>僕は中学3年生で卒業を控えているから、
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>僕は中学三年生で卒業を控えているから、
 タイミング的にはイイと思うけど……</t>
         </is>
       </c>
@@ -3000,7 +3040,7 @@
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>「僕に告白する」という罰ゲームや、
- 何かのイジメなんじゃないだろうか？</t>
+何かのイジメなんじゃないだろうか？</t>
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
@@ -3123,10 +3163,10 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>それじゃ、今日からカップルですね。
- 私たち……</t>
+私たち……</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -3521,9 +3561,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>告白されてから三ヵ月、
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>告白されてから三か月、
 僕らは普通にカップルとして過ごした</t>
         </is>
       </c>
@@ -3623,9 +3663,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>へ？ 罰ゲーム？
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>へ？　罰ゲーム？
 なんの話ですか？</t>
         </is>
       </c>
@@ -3900,9 +3940,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>あれ？ 
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>あれ？
 難しい顔して……どうかしたんですか？</t>
         </is>
       </c>
@@ -7156,9 +7196,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>今、地球に隕石が向かってきています。</t>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>今、地球に隕石が向かってきています</t>
         </is>
       </c>
       <c r="D89" s="6" t="n"/>
@@ -8359,7 +8399,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>５、４、３、２、１、ゼロ</t>
+          <t>5、4、3、2、1、ゼロ</t>
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
@@ -10145,9 +10185,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>そしたら、きっと……私は頑張れます。</t>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>そしたら、きっと……私は頑張れます</t>
         </is>
       </c>
       <c r="D103" s="6" t="n"/>
@@ -11950,9 +11990,9 @@
           <t>砂塚浩二</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>このプランＡがある以上、
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>このプランAがある以上、
 『種』として、人類の存続は可能だ</t>
         </is>
       </c>
@@ -12890,9 +12930,9 @@
           <t>スタッフ</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>５、４、３、２、１、ゼロ……！</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>5、4、3、2、1、ゼロ……！</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
@@ -13144,9 +13184,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>効いていないわけじゃないんでしょう⁉
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>効いていないわけじゃないんでしょう！？
 8％でも削れたのなら、撃ち続ければいい！</t>
         </is>
       </c>
@@ -13612,9 +13652,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>だから何です⁉
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>だから何です！？
 今さら諦めるのはダメですよ！</t>
         </is>
       </c>
@@ -13802,9 +13842,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>痛くない！　痛くないです！　
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>痛くない！　痛くないです！
 こんなの全然痛くありません！</t>
         </is>
       </c>
@@ -13826,10 +13866,10 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>そ、それより！
-光線の威力は上げられないんですか⁉</t>
+光線の威力は上げられないんですか！？</t>
         </is>
       </c>
       <c r="D48" s="6" t="n"/>
@@ -14006,9 +14046,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>奏、死ぬんだぞ⁉</t>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>奏、死ぬんだぞ！？</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -14606,10 +14646,10 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>奏を中心に、
-半径１メートルほどの穴ができていた</t>
+半径1メートルほどの穴ができていた</t>
         </is>
       </c>
       <c r="D78" s="6" t="n"/>
@@ -15308,9 +15348,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>さっさと要件を言え</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>さっさと用件を言え</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -16271,9 +16311,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>結城さん……⁉</t>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>結城さん……！？</t>
         </is>
       </c>
       <c r="D47" s="6" t="n"/>
@@ -19627,7 +19667,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>それじゃ、今日からカップルですね。 私た…</t>
+          <t>それじゃ、今日からカップルですね。私たち…</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -19802,7 +19842,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>へ？ 罰ゲーム？なんの話ですか？</t>
+          <t>へ？　罰ゲーム？なんの話ですか？</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -19952,7 +19992,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>あれ？ 難しい顔して……どうかしたんです…</t>
+          <t>あれ？難しい顔して……どうかしたんですか…</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -21727,7 +21767,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>今、地球に隕石が向かってきています。</t>
+          <t>今、地球に隕石が向かってきています</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -23127,7 +23167,7 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>そしたら、きっと……私は頑張れます。</t>
+          <t>そしたら、きっと……私は頑張れます</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -24527,7 +24567,7 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>効いていないわけじゃないんでしょう⁉8％…</t>
+          <t>効いていないわけじゃないんでしょう！？8…</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
@@ -24777,7 +24817,7 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>だから何です⁉今さら諦めるのはダメですよ…</t>
+          <t>だから何です！？今さら諦めるのはダメです…</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
@@ -24877,7 +24917,7 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>痛くない！　痛くないです！　こんなの全然…</t>
+          <t>痛くない！　痛くないです！こんなの全然痛…</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">

--- a/docs/【キャラ_003】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_003】ときめきポケット_03稿.xlsx
@@ -1400,12 +1400,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>直さずに指摘のみ（omen決定）</t>
+          <t>距離感を表す意図のため現状のまま（omen決定）</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>対応不要</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach.jpg／beach_nonstone.jpg）のまま。夜にする場合は4話の「浜辺（夜）」と同じ扱い</t>
+          <t>夜にする（omen決定）。69は背景：浜辺（夜・岩あり）（beach_night_stone.jpg、新規・要調達）、95は4話29と同じ背景：浜辺（夜）（beach_night.jpg）。昼の beach.jpg・beach_nonstone.jpg は使わない</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>例：砂塚の台詞を「明日の訓練は中止するか？」にする</t>
+          <t>奏の67を「やりましょう。¶もう平気ですから」に変更（「いいえ、」を削除し、1行目の末尾に句点）。砂塚の66は変更なし（omen決定）</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       <c r="E71" s="6" t="n"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩あり）
+          <t>背景：浜辺（夜・岩あり）
 SE：波の音（ループ）</t>
         </is>
       </c>
@@ -7421,7 +7421,7 @@
           <t>SE：爆発
 画面揺れ（大）
 暗転明け
-背景：浜辺（岩なし）</t>
+背景：浜辺（夜）</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -9342,9 +9342,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>いいえ、やりましょう
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>やりましょう。
 もう平気ですから</t>
         </is>
       </c>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>02稿に背景の指定なし。2話で岩を壊したあとの浜辺の夜（浜辺（岩なし）の夜差分）</t>
+          <t>02稿に背景の指定なし。2話95と同じ『浜辺（夜）』を使う</t>
         </is>
       </c>
       <c r="H31" s="6" t="n"/>
@@ -16948,7 +16948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17811,17 +17811,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>浜辺（岩あり）</t>
+          <t>浜辺（夜・岩あり）</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩あり）</t>
+          <t>背景：浜辺（夜・岩あり）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>beach.jpg</t>
+          <t>beach_night_stone.jpg</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach）。見上げるほど大きな岩がある</t>
+          <t>02稿の beach.jpg を夜に変更（omen決定）。見上げるほど大きな岩がある</t>
         </is>
       </c>
     </row>
@@ -17848,17 +17848,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>浜辺（岩なし）</t>
+          <t>浜辺（夜）</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩なし）</t>
+          <t>背景：浜辺（夜）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>beach_nonstone.jpg</t>
+          <t>beach_night.jpg</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2話:95</t>
+          <t>2話:95 / 4話:29</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach_nonstone）。岩を消したあと</t>
+          <t>岩を消したあとの夜の浜辺。2話95〜（02稿の beach_nonstone.jpg を夜に変更）と4話29で共用</t>
         </is>
       </c>
     </row>
@@ -17885,17 +17885,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>浜辺（夜）</t>
+          <t>施設内の部屋（朝）</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（夜）</t>
+          <t>背景：施設内の部屋（朝）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>beach_night.jpg</t>
+          <t>facility_room.jpg</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -17905,12 +17905,12 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>4話:29</t>
+          <t>3話:5</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>「浜辺（岩なし）」の夜差分（4話）</t>
+          <t>島の施設で暮らす部屋。cell.jpg で代用も可</t>
         </is>
       </c>
     </row>
@@ -17922,17 +17922,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>施設内の部屋（朝）</t>
+          <t>砂浜の発射台</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>背景：施設内の部屋（朝）</t>
+          <t>背景：砂浜の発射台</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>facility_room.jpg</t>
+          <t>launch_pad.jpg</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -17942,12 +17942,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>3話:5</t>
+          <t>3話:20</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>島の施設で暮らす部屋。cell.jpg で代用も可</t>
+          <t>砂浜のコンクリートの足場と、右手を固定する金具つきの金属製の椅子</t>
         </is>
       </c>
     </row>
@@ -17959,17 +17959,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>砂浜の発射台</t>
+          <t>砂浜の発射台（焼け跡）</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>背景：砂浜の発射台</t>
+          <t>背景：砂浜の発射台（焼け跡）</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>launch_pad.jpg</t>
+          <t>launch_pad_burnt.jpg</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -17979,12 +17979,12 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>3話:20</t>
+          <t>5話:75</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>砂浜のコンクリートの足場と、右手を固定する金具つきの金属製の椅子</t>
+          <t>「砂浜の発射台」の差分。奏を中心に半径1メートルほどの穴が開き、椅子も器具も熔けて燃え尽きている（5話75〜）</t>
         </is>
       </c>
     </row>
@@ -17996,17 +17996,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>砂浜の発射台（焼け跡）</t>
+          <t>管制室</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>背景：砂浜の発射台（焼け跡）</t>
+          <t>背景：管制室</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>launch_pad_burnt.jpg</t>
+          <t>control_room.jpg</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -18016,12 +18016,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>5話:75</t>
+          <t>3話:35 / 5話:1</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>「砂浜の発射台」の差分。奏を中心に半径1メートルほどの穴が開き、椅子も器具も熔けて燃え尽きている（5話75〜）</t>
+          <t>実験・迎撃を見守る部屋。モニターと機器</t>
         </is>
       </c>
     </row>
@@ -18033,17 +18033,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>管制室</t>
+          <t>医務室</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>背景：管制室</t>
+          <t>背景：医務室</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>control_room.jpg</t>
+          <t>infirmary.jpg</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -18053,12 +18053,12 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>3話:35 / 5話:1</t>
+          <t>3話:50 / 4話:1</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>実験・迎撃を見守る部屋。モニターと機器</t>
+          <t>ベッドのある医務室。3話の「病室」と共用</t>
         </is>
       </c>
     </row>
@@ -18070,32 +18070,32 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>医務室</t>
+          <t>都会の街並み</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>背景：医務室</t>
+          <t>背景：都会の街並み</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>infirmary.jpg</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>city.jpg</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>3話:50 / 4話:1</t>
+          <t>6話:1,62</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>ベッドのある医務室。3話の「病室」と共用</t>
+          <t>1章で使用済み。6話の14年後の東京</t>
         </is>
       </c>
     </row>
@@ -18107,32 +18107,32 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>都会の街並み</t>
+          <t>喫茶店</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>背景：都会の街並み</t>
+          <t>背景：喫茶店</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>city.jpg</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>cafe.jpg</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>6話:1,62</t>
+          <t>6話:5,46</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>1章で使用済み。6話の14年後の東京</t>
+          <t>東京の喫茶店。窓から外の通学路が見える</t>
         </is>
       </c>
     </row>
@@ -18144,17 +18144,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>喫茶店</t>
+          <t>一枚絵</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>背景：喫茶店</t>
+          <t>一枚絵：窓越しの奏</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>cafe.jpg</t>
+          <t>event_003.jpg</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -18164,49 +18164,49 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>6話:5,46</t>
+          <t>6話:44</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>東京の喫茶店。窓から外の通学路が見える</t>
+          <t>喫茶店の窓越しに見える、幸せそうな14歳の奏（02稿の指定）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>BGM</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>一枚絵</t>
+          <t>既存曲（BGM6）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>一枚絵：窓越しの奏</t>
+          <t>夏の眠り</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>event_003.jpg</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>natsunonemuri.ogg</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>6話:44</t>
+          <t>1話:1 / 2話:96 / 3話:1 / 4話:1 / 6話:1</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>喫茶店の窓越しに見える、幸せそうな14歳の奏（02稿の指定）</t>
+          <t>静かでノスタルジック。各話の冒頭、モノローグ</t>
         </is>
       </c>
     </row>
@@ -18218,17 +18218,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM6）</t>
+          <t>既存曲（BGM1）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>夏の眠り</t>
+          <t>ドリーミン</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>natsunonemuri.ogg</t>
+          <t>dreaming.ogg</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -18238,12 +18238,12 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>1話:1 / 2話:96 / 3話:1 / 4話:1 / 6話:1</t>
+          <t>1話:45 / 6話:62</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>静かでノスタルジック。各話の冒頭、モノローグ</t>
+          <t>夏休み前の帰り道（1話）、奏を見送るラスト（6話）</t>
         </is>
       </c>
     </row>
@@ -18255,17 +18255,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM1）</t>
+          <t>既存曲（BGM7）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>ドリーミン</t>
+          <t>ピクニックに行こう</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>dreaming.ogg</t>
+          <t>pikunikkuniikou.ogg</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -18275,12 +18275,12 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>1話:45 / 6話:62</t>
+          <t>3話:5</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>夏休み前の帰り道（1話）、奏を見送るラスト（6話）</t>
+          <t>施設での明るい朝（3話）</t>
         </is>
       </c>
     </row>
@@ -18292,17 +18292,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM7）</t>
+          <t>既存曲（BGM2）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>ピクニックに行こう</t>
+          <t>不可思議話</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>pikunikkuniikou.ogg</t>
+          <t>hukashigibanashi.ogg</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>3話:5</t>
+          <t>1話:92 / 2話:1 / 3話:42,50 / 4話:48</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>施設での明るい朝（3話）</t>
+          <t>緊張・不穏。連行、真相の説明、異変、砂塚との対立</t>
         </is>
       </c>
     </row>
@@ -18329,17 +18329,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM2）</t>
+          <t>既存曲（BGM3）</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>不可思議話</t>
+          <t>変わりゆく街</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>hukashigibanashi.ogg</t>
+          <t>kawariyukumachi.ogg</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>1話:92 / 2話:1 / 3話:42,50 / 4話:48</t>
+          <t>6話:5</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>緊張・不穏。連行、真相の説明、異変、砂塚との対立</t>
+          <t>14年後の喫茶店での砂塚との話（6話）</t>
         </is>
       </c>
     </row>
@@ -18366,17 +18366,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM3）</t>
+          <t>既存曲（BGM8）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>変わりゆく街</t>
+          <t>線香花火</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>kawariyukumachi.ogg</t>
+          <t>senkouhanabi.ogg</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -18386,12 +18386,12 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>6話:5</t>
+          <t>3話:84 / 4話:29,67 / 5話:79 / 6話:44</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>14年後の喫茶店での砂塚との話（6話）</t>
+          <t>切ない。奏の本音（3話）、夜の浜辺（4話）、最期（5話）、窓越しの奏（6話）</t>
         </is>
       </c>
     </row>
@@ -18403,32 +18403,32 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM8）</t>
+          <t>曲調で仮指定</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>線香花火</t>
+          <t>仮BGM_緊迫</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>senkouhanabi.ogg</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>要調達（選曲）</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>3話:84 / 4話:29,67 / 5話:79 / 6話:44</t>
+          <t>2話:87 / 3話:20 / 5話:1</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>切ない。奏の本音（3話）、夜の浜辺（4話）、最期（5話）、窓越しの奏（6話）</t>
+          <t>張り詰めた緊張感。隕石の話、実験、カウントダウン。2章用に登録済みの「BGM_緊迫」（Devil Disaster）の流用も候補</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_緊迫</t>
+          <t>仮BGM_クライマックス</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -18460,49 +18460,49 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>2話:87 / 3話:20 / 5話:1</t>
+          <t>5話:33</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>張り詰めた緊張感。隕石の話、実験、カウントダウン。2章用に登録済みの「BGM_緊迫」（Devil Disaster）の流用も候補</t>
+          <t>5話の迎撃。悲壮で壮大な曲</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>効果音</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_クライマックス</t>
+          <t>プラズマ音</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>plasma.ogg</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>要調達（選曲）</t>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>5話:33</t>
+          <t>2話:92 / 3話:33 / 5話:11,62</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>5話の迎撃。悲壮で壮大な曲</t>
+          <t>02稿の指定。奏の全身に稲妻が走る</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>プラズマ音</t>
+          <t>ビーム音</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>plasma.ogg</t>
+          <t>beam.ogg</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>2話:92 / 3話:33 / 5話:11,62</t>
+          <t>2話:94 / 3話:34 / 5話:11,34,69</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定。奏の全身に稲妻が走る</t>
+          <t>02稿の指定。光線の発射。「ビーム音（連射）」は同じ音を続けて鳴らす</t>
         </is>
       </c>
     </row>
@@ -18556,27 +18556,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>ビーム音</t>
+          <t>爆発</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>beam.ogg</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>explosion.mp3</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>2話:94 / 3話:34 / 5話:11,34,69</t>
+          <t>2話:95</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定。光線の発射。「ビーム音（連射）」は同じ音を続けて鳴らす</t>
+          <t>2章で使用済み。02稿の「爆発音」</t>
         </is>
       </c>
     </row>
@@ -18593,27 +18593,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>爆発</t>
+          <t>波の音</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>explosion.mp3</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>wave.ogg</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>2話:95</t>
+          <t>2話:69 / 3話:20 / 4話:29 / 5話:75</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み。02稿の「爆発音」</t>
+          <t>ループ。浜辺・発射台</t>
         </is>
       </c>
     </row>
@@ -18630,12 +18630,12 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>波の音</t>
+          <t>機械の駆動音（歯車）</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>wave.ogg</t>
+          <t>machine_gear.ogg</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -18645,12 +18645,12 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>2話:69 / 3話:20 / 4話:29 / 5話:75</t>
+          <t>3話:25</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>ループ。浜辺・発射台</t>
+          <t>右手を固定する器具の歯車がキリキリと回る音（3話）</t>
         </is>
       </c>
     </row>
@@ -18667,12 +18667,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>機械の駆動音（歯車）</t>
+          <t>歓声・拍手</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>machine_gear.ogg</t>
+          <t>cheer.ogg</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -18682,12 +18682,12 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>3話:25</t>
+          <t>3話:37 / 5話:72</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>右手を固定する器具の歯車がキリキリと回る音（3話）</t>
+          <t>管制室の歓声と拍手</t>
         </is>
       </c>
     </row>
@@ -18704,27 +18704,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>歓声・拍手</t>
+          <t>炎が燃える音</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>cheer.ogg</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>fire.mp3</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>3話:37 / 5話:72</t>
+          <t>5話:64</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>管制室の歓声と拍手</t>
+          <t>2章で使用済み。ループ。5話の青い炎</t>
         </is>
       </c>
     </row>
@@ -18741,27 +18741,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>炎が燃える音</t>
+          <t>体が崩れる音</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>fire.mp3</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>crumble.ogg</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>5話:64</t>
+          <t>5話:81,84,91</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み。ループ。5話の青い炎</t>
+          <t>炭になった奏の体が崩れる、乾いた小さめの音</t>
         </is>
       </c>
     </row>
@@ -18778,12 +18778,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>体が崩れる音</t>
+          <t>時計の秒針</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>crumble.ogg</t>
+          <t>clock_tick.ogg</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -18793,12 +18793,12 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>5話:81,84,91</t>
+          <t>3話:109</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>炭になった奏の体が崩れる、乾いた小さめの音</t>
+          <t>ループ。3話の最後</t>
         </is>
       </c>
     </row>
@@ -18815,12 +18815,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>時計の秒針</t>
+          <t>喫茶店の環境音</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>clock_tick.ogg</t>
+          <t>cafe_ambience.ogg</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -18830,12 +18830,12 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>3話:109</t>
+          <t>6話:5</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>ループ。3話の最後</t>
+          <t>ループ。小さめに</t>
         </is>
       </c>
     </row>
@@ -18852,12 +18852,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>喫茶店の環境音</t>
+          <t>雑踏</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>cafe_ambience.ogg</t>
+          <t>crowd.ogg</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -18867,12 +18867,12 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>6話:5</t>
+          <t>6話:1,62</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>ループ。小さめに</t>
+          <t>ループ。東京の街</t>
         </is>
       </c>
     </row>
@@ -18889,27 +18889,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>雑踏</t>
+          <t>車のドア</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>crowd.ogg</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_door.mp3</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>6話:1,62</t>
+          <t>1話:96</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>ループ。東京の街</t>
+          <t>2章で使用済み</t>
         </is>
       </c>
     </row>
@@ -18926,12 +18926,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>車のドア</t>
+          <t>走る足音</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>car_door.mp3</t>
+          <t>Leather_shoes_run.ogg</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -18941,12 +18941,12 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>1話:96</t>
+          <t>5話:74</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み</t>
+          <t>1章で使用済み</t>
         </is>
       </c>
     </row>
@@ -18963,12 +18963,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>走る足音</t>
+          <t>歩く足音</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Leather_shoes_run.ogg</t>
+          <t>Leather_shoes_walk.ogg</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>5話:74</t>
+          <t>1話:42 / 2話:67 / 4話:48</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -18990,37 +18990,33 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>演出</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>効果音</t>
+          <t>宴の標準機能</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>歩く足音</t>
+          <t>画面揺れ（小／大）</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Leather_shoes_walk.ogg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>既存</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>1話:42 / 2話:67 / 4話:48</t>
-        </is>
-      </c>
+          <t>素材不要</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n"/>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>1章で使用済み</t>
+          <t>光線の発射は大、異変・崩れる場面は小</t>
         </is>
       </c>
     </row>
@@ -19037,7 +19033,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>画面揺れ（小／大）</t>
+          <t>白フラッシュ（ホワイトアウト）</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -19053,7 +19049,7 @@
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>光線の発射は大、異変・崩れる場面は小</t>
+          <t>光線の発射</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19066,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>白フラッシュ（ホワイトアウト）</t>
+          <t>暗転／暗転明け</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -19084,11 +19080,7 @@
         </is>
       </c>
       <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>光線の発射</t>
-        </is>
-      </c>
+      <c r="G58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -19103,7 +19095,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>暗転／暗転明け</t>
+          <t>フェードアウト</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -19117,69 +19109,40 @@
         </is>
       </c>
       <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>3話・5話・6話の終わり</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>演出</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>宴の標準機能</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>フェードアウト</t>
+          <t>メッセージボックス・選択ボタン</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1章と共通</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>素材不要</t>
+          <t>既存</t>
         </is>
       </c>
       <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>3話・5話・6話の終わり</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>メッセージボックス・選択ボタン</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>1章と共通</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22467,7 +22430,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>いいえ、やりましょうもう平気ですから</t>
+          <t>やりましょう。もう平気ですから</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">

--- a/docs/【キャラ_003】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_003】ときめきポケット_03稿.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>直さずに指摘のみ（omen決定）</t>
+          <t>距離感を表す意図のため現状のまま（omen決定）</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>対応不要</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach.jpg／beach_nonstone.jpg）のまま。夜にする場合は4話の「浜辺（夜）」と同じ扱い</t>
+          <t>夜にする（omen決定）。69は背景：浜辺（夜・岩あり）（beach_night_stone.jpg、新規・要調達）、95は4話29と同じ背景：浜辺（夜）（beach_night.jpg）。昼の beach.jpg・beach_nonstone.jpg は使わない</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>20を「中学三年生」（漢数字）に統一</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>48を「三か月」に統一</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>59を「プランA」（半角）に統一</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>どちらかに統一</t>
+          <t>半角に統一（3話32・5話10を「5、4、3、2、1、ゼロ」、5話76を「1メートル」に）</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>「！？」に統一</t>
+          <t>「！？」（全角2文字）に統一</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>空白を削除、または全角スペースに統一</t>
+          <t>1話29・34の行頭の半角スペースを削除、1話52「へ？ 」の半角スペースを全角スペースに。1話63・5話45：行末の空白を削除</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>例：砂塚の台詞を「明日の訓練は中止するか？」にする</t>
+          <t>奏の67を「やりましょう。¶もう平気ですから」に変更（「いいえ、」を削除し、1行目の末尾に句点）。砂塚の66は変更なし（omen決定）</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>指摘のみ（未対応）</t>
+          <t>反映済み</t>
         </is>
       </c>
     </row>
@@ -2206,6 +2206,46 @@
       <c r="H38" s="6" t="inlineStr">
         <is>
           <t>演出で対応済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>1話・2話</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1話11 / 2話98</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>1話11 / 2話98</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>書式</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>1話11・2話98『結城 奏』の名前の中の半角スペース</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>姓と名の区切りとして残す（omen決定）</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>対応不要</t>
         </is>
       </c>
     </row>
@@ -2649,10 +2689,10 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>結城さんは物静かで、
-そう言う事には関心がないと思っていた</t>
+そういう事には関心がないと思っていた</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
@@ -2769,9 +2809,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>僕は中学3年生で卒業を控えているから、
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>僕は中学三年生で卒業を控えているから、
 タイミング的にはイイと思うけど……</t>
         </is>
       </c>
@@ -3000,7 +3040,7 @@
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>「僕に告白する」という罰ゲームや、
- 何かのイジメなんじゃないだろうか？</t>
+何かのイジメなんじゃないだろうか？</t>
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
@@ -3123,10 +3163,10 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>それじゃ、今日からカップルですね。
- 私たち……</t>
+私たち……</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -3521,9 +3561,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>告白されてから三ヵ月、
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>告白されてから三か月、
 僕らは普通にカップルとして過ごした</t>
         </is>
       </c>
@@ -3623,9 +3663,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>へ？ 罰ゲーム？
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>へ？　罰ゲーム？
 なんの話ですか？</t>
         </is>
       </c>
@@ -3900,9 +3940,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>あれ？ 
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>あれ？
 難しい顔して……どうかしたんですか？</t>
         </is>
       </c>
@@ -6716,7 +6756,7 @@
       <c r="E71" s="6" t="n"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩あり）
+          <t>背景：浜辺（夜・岩あり）
 SE：波の音（ループ）</t>
         </is>
       </c>
@@ -7156,9 +7196,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>今、地球に隕石が向かってきています。</t>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>今、地球に隕石が向かってきています</t>
         </is>
       </c>
       <c r="D89" s="6" t="n"/>
@@ -7381,7 +7421,7 @@
           <t>SE：爆発
 画面揺れ（大）
 暗転明け
-背景：浜辺（岩なし）</t>
+背景：浜辺（夜）</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -8359,7 +8399,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>５、４、３、２、１、ゼロ</t>
+          <t>5、4、3、2、1、ゼロ</t>
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
@@ -9302,9 +9342,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>いいえ、やりましょう
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>やりましょう。
 もう平気ですから</t>
         </is>
       </c>
@@ -10145,9 +10185,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>そしたら、きっと……私は頑張れます。</t>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>そしたら、きっと……私は頑張れます</t>
         </is>
       </c>
       <c r="D103" s="6" t="n"/>
@@ -11211,7 +11251,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>02稿に背景の指定なし。2話で岩を壊したあとの浜辺の夜（浜辺（岩なし）の夜差分）</t>
+          <t>02稿に背景の指定なし。2話95と同じ『浜辺（夜）』を使う</t>
         </is>
       </c>
       <c r="H31" s="6" t="n"/>
@@ -11950,9 +11990,9 @@
           <t>砂塚浩二</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>このプランＡがある以上、
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>このプランAがある以上、
 『種』として、人類の存続は可能だ</t>
         </is>
       </c>
@@ -12890,9 +12930,9 @@
           <t>スタッフ</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>５、４、３、２、１、ゼロ……！</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>5、4、3、2、1、ゼロ……！</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
@@ -13144,9 +13184,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>効いていないわけじゃないんでしょう⁉
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>効いていないわけじゃないんでしょう！？
 8％でも削れたのなら、撃ち続ければいい！</t>
         </is>
       </c>
@@ -13612,9 +13652,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>だから何です⁉
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>だから何です！？
 今さら諦めるのはダメですよ！</t>
         </is>
       </c>
@@ -13802,9 +13842,9 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>痛くない！　痛くないです！　
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>痛くない！　痛くないです！
 こんなの全然痛くありません！</t>
         </is>
       </c>
@@ -13826,10 +13866,10 @@
           <t>結城奏</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>そ、それより！
-光線の威力は上げられないんですか⁉</t>
+光線の威力は上げられないんですか！？</t>
         </is>
       </c>
       <c r="D48" s="6" t="n"/>
@@ -14006,9 +14046,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>奏、死ぬんだぞ⁉</t>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>奏、死ぬんだぞ！？</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -14606,10 +14646,10 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>奏を中心に、
-半径１メートルほどの穴ができていた</t>
+半径1メートルほどの穴ができていた</t>
         </is>
       </c>
       <c r="D78" s="6" t="n"/>
@@ -15308,9 +15348,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>さっさと要件を言え</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>さっさと用件を言え</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -16271,9 +16311,9 @@
           <t>主人公</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>結城さん……⁉</t>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>結城さん……！？</t>
         </is>
       </c>
       <c r="D47" s="6" t="n"/>
@@ -16908,7 +16948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17771,17 +17811,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>浜辺（岩あり）</t>
+          <t>浜辺（夜・岩あり）</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩あり）</t>
+          <t>背景：浜辺（夜・岩あり）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>beach.jpg</t>
+          <t>beach_night_stone.jpg</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -17796,7 +17836,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach）。見上げるほど大きな岩がある</t>
+          <t>02稿の beach.jpg を夜に変更（omen決定）。見上げるほど大きな岩がある</t>
         </is>
       </c>
     </row>
@@ -17808,17 +17848,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>浜辺（岩なし）</t>
+          <t>浜辺（夜）</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（岩なし）</t>
+          <t>背景：浜辺（夜）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>beach_nonstone.jpg</t>
+          <t>beach_night.jpg</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -17828,12 +17868,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2話:95</t>
+          <t>2話:95 / 4話:29</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定（beach_nonstone）。岩を消したあと</t>
+          <t>岩を消したあとの夜の浜辺。2話95〜（02稿の beach_nonstone.jpg を夜に変更）と4話29で共用</t>
         </is>
       </c>
     </row>
@@ -17845,17 +17885,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>浜辺（夜）</t>
+          <t>施設内の部屋（朝）</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>背景：浜辺（夜）</t>
+          <t>背景：施設内の部屋（朝）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>beach_night.jpg</t>
+          <t>facility_room.jpg</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -17865,12 +17905,12 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>4話:29</t>
+          <t>3話:5</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>「浜辺（岩なし）」の夜差分（4話）</t>
+          <t>島の施設で暮らす部屋。cell.jpg で代用も可</t>
         </is>
       </c>
     </row>
@@ -17882,17 +17922,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>施設内の部屋（朝）</t>
+          <t>砂浜の発射台</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>背景：施設内の部屋（朝）</t>
+          <t>背景：砂浜の発射台</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>facility_room.jpg</t>
+          <t>launch_pad.jpg</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -17902,12 +17942,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>3話:5</t>
+          <t>3話:20</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>島の施設で暮らす部屋。cell.jpg で代用も可</t>
+          <t>砂浜のコンクリートの足場と、右手を固定する金具つきの金属製の椅子</t>
         </is>
       </c>
     </row>
@@ -17919,17 +17959,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>砂浜の発射台</t>
+          <t>砂浜の発射台（焼け跡）</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>背景：砂浜の発射台</t>
+          <t>背景：砂浜の発射台（焼け跡）</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>launch_pad.jpg</t>
+          <t>launch_pad_burnt.jpg</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -17939,12 +17979,12 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>3話:20</t>
+          <t>5話:75</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>砂浜のコンクリートの足場と、右手を固定する金具つきの金属製の椅子</t>
+          <t>「砂浜の発射台」の差分。奏を中心に半径1メートルほどの穴が開き、椅子も器具も熔けて燃え尽きている（5話75〜）</t>
         </is>
       </c>
     </row>
@@ -17956,17 +17996,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>砂浜の発射台（焼け跡）</t>
+          <t>管制室</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>背景：砂浜の発射台（焼け跡）</t>
+          <t>背景：管制室</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>launch_pad_burnt.jpg</t>
+          <t>control_room.jpg</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -17976,12 +18016,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>5話:75</t>
+          <t>3話:35 / 5話:1</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>「砂浜の発射台」の差分。奏を中心に半径1メートルほどの穴が開き、椅子も器具も熔けて燃え尽きている（5話75〜）</t>
+          <t>実験・迎撃を見守る部屋。モニターと機器</t>
         </is>
       </c>
     </row>
@@ -17993,17 +18033,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>管制室</t>
+          <t>医務室</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>背景：管制室</t>
+          <t>背景：医務室</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>control_room.jpg</t>
+          <t>infirmary.jpg</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -18013,12 +18053,12 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>3話:35 / 5話:1</t>
+          <t>3話:50 / 4話:1</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>実験・迎撃を見守る部屋。モニターと機器</t>
+          <t>ベッドのある医務室。3話の「病室」と共用</t>
         </is>
       </c>
     </row>
@@ -18030,32 +18070,32 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>医務室</t>
+          <t>都会の街並み</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>背景：医務室</t>
+          <t>背景：都会の街並み</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>infirmary.jpg</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>city.jpg</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>3話:50 / 4話:1</t>
+          <t>6話:1,62</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>ベッドのある医務室。3話の「病室」と共用</t>
+          <t>1章で使用済み。6話の14年後の東京</t>
         </is>
       </c>
     </row>
@@ -18067,32 +18107,32 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>都会の街並み</t>
+          <t>喫茶店</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>背景：都会の街並み</t>
+          <t>背景：喫茶店</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>city.jpg</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>cafe.jpg</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>6話:1,62</t>
+          <t>6話:5,46</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>1章で使用済み。6話の14年後の東京</t>
+          <t>東京の喫茶店。窓から外の通学路が見える</t>
         </is>
       </c>
     </row>
@@ -18104,17 +18144,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>喫茶店</t>
+          <t>一枚絵</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>背景：喫茶店</t>
+          <t>一枚絵：窓越しの奏</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>cafe.jpg</t>
+          <t>event_003.jpg</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -18124,49 +18164,49 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>6話:5,46</t>
+          <t>6話:44</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>東京の喫茶店。窓から外の通学路が見える</t>
+          <t>喫茶店の窓越しに見える、幸せそうな14歳の奏（02稿の指定）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>BGM</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>一枚絵</t>
+          <t>既存曲（BGM6）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>一枚絵：窓越しの奏</t>
+          <t>夏の眠り</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>event_003.jpg</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>natsunonemuri.ogg</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>6話:44</t>
+          <t>1話:1 / 2話:96 / 3話:1 / 4話:1 / 6話:1</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>喫茶店の窓越しに見える、幸せそうな14歳の奏（02稿の指定）</t>
+          <t>静かでノスタルジック。各話の冒頭、モノローグ</t>
         </is>
       </c>
     </row>
@@ -18178,17 +18218,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM6）</t>
+          <t>既存曲（BGM1）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>夏の眠り</t>
+          <t>ドリーミン</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>natsunonemuri.ogg</t>
+          <t>dreaming.ogg</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -18198,12 +18238,12 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>1話:1 / 2話:96 / 3話:1 / 4話:1 / 6話:1</t>
+          <t>1話:45 / 6話:62</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>静かでノスタルジック。各話の冒頭、モノローグ</t>
+          <t>夏休み前の帰り道（1話）、奏を見送るラスト（6話）</t>
         </is>
       </c>
     </row>
@@ -18215,17 +18255,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM1）</t>
+          <t>既存曲（BGM7）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>ドリーミン</t>
+          <t>ピクニックに行こう</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>dreaming.ogg</t>
+          <t>pikunikkuniikou.ogg</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -18235,12 +18275,12 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>1話:45 / 6話:62</t>
+          <t>3話:5</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>夏休み前の帰り道（1話）、奏を見送るラスト（6話）</t>
+          <t>施設での明るい朝（3話）</t>
         </is>
       </c>
     </row>
@@ -18252,17 +18292,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM7）</t>
+          <t>既存曲（BGM2）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>ピクニックに行こう</t>
+          <t>不可思議話</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>pikunikkuniikou.ogg</t>
+          <t>hukashigibanashi.ogg</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -18272,12 +18312,12 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>3話:5</t>
+          <t>1話:92 / 2話:1 / 3話:42,50 / 4話:48</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>施設での明るい朝（3話）</t>
+          <t>緊張・不穏。連行、真相の説明、異変、砂塚との対立</t>
         </is>
       </c>
     </row>
@@ -18289,17 +18329,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM2）</t>
+          <t>既存曲（BGM3）</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>不可思議話</t>
+          <t>変わりゆく街</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>hukashigibanashi.ogg</t>
+          <t>kawariyukumachi.ogg</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -18309,12 +18349,12 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>1話:92 / 2話:1 / 3話:42,50 / 4話:48</t>
+          <t>6話:5</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>緊張・不穏。連行、真相の説明、異変、砂塚との対立</t>
+          <t>14年後の喫茶店での砂塚との話（6話）</t>
         </is>
       </c>
     </row>
@@ -18326,17 +18366,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM3）</t>
+          <t>既存曲（BGM8）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>変わりゆく街</t>
+          <t>線香花火</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>kawariyukumachi.ogg</t>
+          <t>senkouhanabi.ogg</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -18346,12 +18386,12 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>6話:5</t>
+          <t>3話:84 / 4話:29,67 / 5話:79 / 6話:44</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>14年後の喫茶店での砂塚との話（6話）</t>
+          <t>切ない。奏の本音（3話）、夜の浜辺（4話）、最期（5話）、窓越しの奏（6話）</t>
         </is>
       </c>
     </row>
@@ -18363,32 +18403,32 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>既存曲（BGM8）</t>
+          <t>曲調で仮指定</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>線香花火</t>
+          <t>仮BGM_緊迫</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>senkouhanabi.ogg</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>要調達（選曲）</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>3話:84 / 4話:29,67 / 5話:79 / 6話:44</t>
+          <t>2話:87 / 3話:20 / 5話:1</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>切ない。奏の本音（3話）、夜の浜辺（4話）、最期（5話）、窓越しの奏（6話）</t>
+          <t>張り詰めた緊張感。隕石の話、実験、カウントダウン。2章用に登録済みの「BGM_緊迫」（Devil Disaster）の流用も候補</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18445,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_緊迫</t>
+          <t>仮BGM_クライマックス</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -18420,49 +18460,49 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>2話:87 / 3話:20 / 5話:1</t>
+          <t>5話:33</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>張り詰めた緊張感。隕石の話、実験、カウントダウン。2章用に登録済みの「BGM_緊迫」（Devil Disaster）の流用も候補</t>
+          <t>5話の迎撃。悲壮で壮大な曲</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>効果音</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_クライマックス</t>
+          <t>プラズマ音</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>plasma.ogg</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>要調達（選曲）</t>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>5話:33</t>
+          <t>2話:92 / 3話:33 / 5話:11,62</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>5話の迎撃。悲壮で壮大な曲</t>
+          <t>02稿の指定。奏の全身に稲妻が走る</t>
         </is>
       </c>
     </row>
@@ -18479,12 +18519,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>プラズマ音</t>
+          <t>ビーム音</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>plasma.ogg</t>
+          <t>beam.ogg</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -18494,12 +18534,12 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>2話:92 / 3話:33 / 5話:11,62</t>
+          <t>2話:94 / 3話:34 / 5話:11,34,69</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定。奏の全身に稲妻が走る</t>
+          <t>02稿の指定。光線の発射。「ビーム音（連射）」は同じ音を続けて鳴らす</t>
         </is>
       </c>
     </row>
@@ -18516,27 +18556,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>ビーム音</t>
+          <t>爆発</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>beam.ogg</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>explosion.mp3</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>2話:94 / 3話:34 / 5話:11,34,69</t>
+          <t>2話:95</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>02稿の指定。光線の発射。「ビーム音（連射）」は同じ音を続けて鳴らす</t>
+          <t>2章で使用済み。02稿の「爆発音」</t>
         </is>
       </c>
     </row>
@@ -18553,27 +18593,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>爆発</t>
+          <t>波の音</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>explosion.mp3</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>wave.ogg</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>2話:95</t>
+          <t>2話:69 / 3話:20 / 4話:29 / 5話:75</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み。02稿の「爆発音」</t>
+          <t>ループ。浜辺・発射台</t>
         </is>
       </c>
     </row>
@@ -18590,12 +18630,12 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>波の音</t>
+          <t>機械の駆動音（歯車）</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>wave.ogg</t>
+          <t>machine_gear.ogg</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -18605,12 +18645,12 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>2話:69 / 3話:20 / 4話:29 / 5話:75</t>
+          <t>3話:25</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>ループ。浜辺・発射台</t>
+          <t>右手を固定する器具の歯車がキリキリと回る音（3話）</t>
         </is>
       </c>
     </row>
@@ -18627,12 +18667,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>機械の駆動音（歯車）</t>
+          <t>歓声・拍手</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>machine_gear.ogg</t>
+          <t>cheer.ogg</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -18642,12 +18682,12 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>3話:25</t>
+          <t>3話:37 / 5話:72</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>右手を固定する器具の歯車がキリキリと回る音（3話）</t>
+          <t>管制室の歓声と拍手</t>
         </is>
       </c>
     </row>
@@ -18664,27 +18704,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>歓声・拍手</t>
+          <t>炎が燃える音</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>cheer.ogg</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>fire.mp3</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>3話:37 / 5話:72</t>
+          <t>5話:64</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>管制室の歓声と拍手</t>
+          <t>2章で使用済み。ループ。5話の青い炎</t>
         </is>
       </c>
     </row>
@@ -18701,27 +18741,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>炎が燃える音</t>
+          <t>体が崩れる音</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>fire.mp3</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
+          <t>crumble.ogg</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>要調達</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>5話:64</t>
+          <t>5話:81,84,91</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み。ループ。5話の青い炎</t>
+          <t>炭になった奏の体が崩れる、乾いた小さめの音</t>
         </is>
       </c>
     </row>
@@ -18738,12 +18778,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>体が崩れる音</t>
+          <t>時計の秒針</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>crumble.ogg</t>
+          <t>clock_tick.ogg</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -18753,12 +18793,12 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>5話:81,84,91</t>
+          <t>3話:109</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>炭になった奏の体が崩れる、乾いた小さめの音</t>
+          <t>ループ。3話の最後</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18815,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>時計の秒針</t>
+          <t>喫茶店の環境音</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>clock_tick.ogg</t>
+          <t>cafe_ambience.ogg</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -18790,12 +18830,12 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>3話:109</t>
+          <t>6話:5</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>ループ。3話の最後</t>
+          <t>ループ。小さめに</t>
         </is>
       </c>
     </row>
@@ -18812,12 +18852,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>喫茶店の環境音</t>
+          <t>雑踏</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>cafe_ambience.ogg</t>
+          <t>crowd.ogg</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -18827,12 +18867,12 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>6話:5</t>
+          <t>6話:1,62</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>ループ。小さめに</t>
+          <t>ループ。東京の街</t>
         </is>
       </c>
     </row>
@@ -18849,27 +18889,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>雑踏</t>
+          <t>車のドア</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>crowd.ogg</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_door.mp3</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>既存</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>6話:1,62</t>
+          <t>1話:96</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>ループ。東京の街</t>
+          <t>2章で使用済み</t>
         </is>
       </c>
     </row>
@@ -18886,12 +18926,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>車のドア</t>
+          <t>走る足音</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>car_door.mp3</t>
+          <t>Leather_shoes_run.ogg</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -18901,12 +18941,12 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>1話:96</t>
+          <t>5話:74</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>2章で使用済み</t>
+          <t>1章で使用済み</t>
         </is>
       </c>
     </row>
@@ -18923,12 +18963,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>走る足音</t>
+          <t>歩く足音</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Leather_shoes_run.ogg</t>
+          <t>Leather_shoes_walk.ogg</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -18938,7 +18978,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>5話:74</t>
+          <t>1話:42 / 2話:67 / 4話:48</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -18950,37 +18990,33 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>演出</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>効果音</t>
+          <t>宴の標準機能</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>歩く足音</t>
+          <t>画面揺れ（小／大）</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Leather_shoes_walk.ogg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>既存</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>1話:42 / 2話:67 / 4話:48</t>
-        </is>
-      </c>
+          <t>素材不要</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n"/>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>1章で使用済み</t>
+          <t>光線の発射は大、異変・崩れる場面は小</t>
         </is>
       </c>
     </row>
@@ -18997,7 +19033,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>画面揺れ（小／大）</t>
+          <t>白フラッシュ（ホワイトアウト）</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -19013,7 +19049,7 @@
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>光線の発射は大、異変・崩れる場面は小</t>
+          <t>光線の発射</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19066,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>白フラッシュ（ホワイトアウト）</t>
+          <t>暗転／暗転明け</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -19044,11 +19080,7 @@
         </is>
       </c>
       <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>光線の発射</t>
-        </is>
-      </c>
+      <c r="G58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -19063,7 +19095,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>暗転／暗転明け</t>
+          <t>フェードアウト</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -19077,69 +19109,40 @@
         </is>
       </c>
       <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>3話・5話・6話の終わり</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>演出</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>宴の標準機能</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>フェードアウト</t>
+          <t>メッセージボックス・選択ボタン</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1章と共通</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>素材不要</t>
+          <t>既存</t>
         </is>
       </c>
       <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>3話・5話・6話の終わり</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>メッセージボックス・選択ボタン</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>1章と共通</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>既存</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19627,7 +19630,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>それじゃ、今日からカップルですね。 私た…</t>
+          <t>それじゃ、今日からカップルですね。私たち…</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -19802,7 +19805,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>へ？ 罰ゲーム？なんの話ですか？</t>
+          <t>へ？　罰ゲーム？なんの話ですか？</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -19952,7 +19955,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>あれ？ 難しい顔して……どうかしたんです…</t>
+          <t>あれ？難しい顔して……どうかしたんですか…</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -21727,7 +21730,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>今、地球に隕石が向かってきています。</t>
+          <t>今、地球に隕石が向かってきています</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -22427,7 +22430,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>いいえ、やりましょうもう平気ですから</t>
+          <t>やりましょう。もう平気ですから</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -23127,7 +23130,7 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>そしたら、きっと……私は頑張れます。</t>
+          <t>そしたら、きっと……私は頑張れます</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -24527,7 +24530,7 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>効いていないわけじゃないんでしょう⁉8％…</t>
+          <t>効いていないわけじゃないんでしょう！？8…</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
@@ -24777,7 +24780,7 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>だから何です⁉今さら諦めるのはダメですよ…</t>
+          <t>だから何です！？今さら諦めるのはダメです…</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
@@ -24877,7 +24880,7 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>痛くない！　痛くないです！　こんなの全然…</t>
+          <t>痛くない！　痛くないです！こんなの全然痛…</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">

--- a/docs/【キャラ_003】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_003】ときめきポケット_03稿.xlsx
@@ -16978,7 +16978,7 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>ファイル名（案）</t>
+          <t>ファイル名</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
@@ -17018,9 +17018,9 @@
           <t>kanade/003_yuki_normal.png</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -17055,9 +17055,9 @@
           <t>kanade/003_yuki_happy.png</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -17092,9 +17092,9 @@
           <t>kanade/003_yuki_angry.png</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -17129,9 +17129,9 @@
           <t>kanade/003_yuki_sad.png</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -17166,9 +17166,9 @@
           <t>kanade/003_yuki_tere.png</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>fire.mp3</t>
+          <t>Ambience/fire.mp3</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">

--- a/docs/【キャラ_003】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_003】ときめきポケット_03稿.xlsx
@@ -17205,7 +17205,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ立ち絵なし）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ立ち絵なし）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ立ち絵なし）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ立ち絵なし）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ悲しみの炭化版で代用）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ立ち絵なし）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -17425,9 +17425,9 @@
           <t>sunazuka/003_sunazuka_normal.png</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -17462,9 +17462,9 @@
           <t>sunazuka/003_sunazuka_stern.png</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -17499,9 +17499,9 @@
           <t>sunazuka/003_sunazuka_old_normal.png</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -17673,12 +17673,12 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>tsugakuro_ch3_evening.jpg</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>tsugakuro_ch3_evening.png</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>residential_evening.jpg</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>residential_evening.png</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -17747,12 +17747,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>cell.jpg</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>cell.png</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -17784,12 +17784,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>album.jpg</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>album.png</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -17821,12 +17821,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>beach_night_stone.jpg</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>beach_night_stone.png</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -17858,12 +17858,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>beach_night.jpg</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>beach_night.png</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17895,12 +17895,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>facility_room.jpg</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>facility_room.png</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -17932,12 +17932,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>launch_pad.jpg</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>launch_pad.png</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17969,12 +17969,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>launch_pad_burnt.jpg</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>launch_pad_burnt.png</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>control_room.jpg</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>control_room.png</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>infirmary.jpg</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>infirmary.png</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -18117,12 +18117,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cafe.jpg</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>cafe.png</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -18157,9 +18157,9 @@
           <t>event_003.jpg</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -18403,22 +18403,22 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_緊迫</t>
+          <t>BGM_緊迫</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>devil_disaster.mp3</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>要調達（選曲）</t>
+          <t>既存</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>張り詰めた緊張感。隕石の話、実験、カウントダウン。2章用に登録済みの「BGM_緊迫」（Devil Disaster）の流用も候補</t>
+          <t>2章のBGM_緊迫（Devil Disaster）を流用。張り詰めた緊張感。隕石の話、実験、カウントダウン。</t>
         </is>
       </c>
     </row>
@@ -18440,22 +18440,22 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_クライマックス</t>
+          <t>BGM_クライマックス</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>will_you_still_cry.mp3</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>5話の迎撃。悲壮で壮大な曲</t>
+          <t>曲名：Will you still cry?（ループ始点 10.847秒）。5話の迎撃。悲壮で壮大な曲</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>plasma.ogg</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>plasma.mp3</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -18524,12 +18524,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>beam.ogg</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>beam.mp3</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -18598,12 +18598,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>wave.ogg</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/wave.mp3</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -18635,12 +18635,12 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>machine_gear.ogg</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>machine_gear.mp3</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -18672,12 +18672,12 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>cheer.ogg</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>cheer.mp3</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>crumble.ogg</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>crumble.mp3</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -18783,12 +18783,12 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>clock_tick.ogg</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/clock_tick.mp3</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -18820,12 +18820,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>cafe_ambience.ogg</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/cafe_ambience.mp3</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -18857,12 +18857,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>crowd.ogg</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/crowd.mp3</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
